--- a/Catch models/msy_resumo_cenarios_dbsra.xlsx
+++ b/Catch models/msy_resumo_cenarios_dbsra.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>cenario_id</t>
   </si>
@@ -37,46 +37,61 @@
     <t>n_aceitos</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Jardim(1996-1999)</t>
+    <t>NN_CMSY_M_Jardim(1981-1994)</t>
   </si>
   <si>
     <t>NN_CMSY</t>
   </si>
   <si>
-    <t>M_Jardim(1996-1999)</t>
-  </si>
-  <si>
-    <t>NN_CMSY_M_Santos(2018)</t>
-  </si>
-  <si>
-    <t>M_Santos(2018)</t>
-  </si>
-  <si>
-    <t>Target_switch_M_Jardim(1996-1999)</t>
+    <t>M_Jardim(1981-1994)</t>
+  </si>
+  <si>
+    <t>NN_CMSY_M_Santos(2005-2018)</t>
+  </si>
+  <si>
+    <t>M_Santos(2005-2018)</t>
+  </si>
+  <si>
+    <t>NN_CMSY_M_Vieira(1988-2018)</t>
+  </si>
+  <si>
+    <t>M_Vieira(1988-2018)</t>
+  </si>
+  <si>
+    <t>Target_switch_M_Jardim(1981-1994)</t>
   </si>
   <si>
     <t>Target_switch</t>
   </si>
   <si>
-    <t>Target_switch_M_Santos(2018)</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_M_Jardim(1996-1999)</t>
+    <t>Target_switch_M_Santos(2005-2018)</t>
+  </si>
+  <si>
+    <t>Target_switch_M_Vieira(1988-2018)</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_M_Jardim(1981-1994)</t>
   </si>
   <si>
     <t>Uninformative_bk</t>
   </si>
   <si>
-    <t>Uninformative_bk_M_Santos(2018)</t>
-  </si>
-  <si>
-    <t>zBRT_M_Jardim(1996-1999)</t>
+    <t>Uninformative_bk_M_Santos(2005-2018)</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_M_Vieira(1988-2018)</t>
+  </si>
+  <si>
+    <t>zBRT_M_Jardim(1981-1994)</t>
   </si>
   <si>
     <t>zBRT</t>
   </si>
   <si>
-    <t>zBRT_M_Santos(2018)</t>
+    <t>zBRT_M_Santos(2005-2018)</t>
+  </si>
+  <si>
+    <t>zBRT_M_Vieira(1988-2018)</t>
   </si>
 </sst>
 </file>
@@ -419,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -456,16 +471,16 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1808.012383372738</v>
+        <v>1896.769409607813</v>
       </c>
       <c r="E2">
-        <v>1399.503251624742</v>
+        <v>1581.59097671675</v>
       </c>
       <c r="F2">
-        <v>2004.366349841148</v>
+        <v>2046.507984910551</v>
       </c>
       <c r="G2">
-        <v>4066</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -479,16 +494,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>1888.443360254738</v>
+        <v>1895.789243182264</v>
       </c>
       <c r="E3">
-        <v>1580.646549439267</v>
+        <v>1591.736666665113</v>
       </c>
       <c r="F3">
-        <v>2045.940136011736</v>
+        <v>2048.019297247105</v>
       </c>
       <c r="G3">
-        <v>3392</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -496,22 +511,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
       <c r="D4">
-        <v>2062.595206710932</v>
+        <v>1942.305860762551</v>
       </c>
       <c r="E4">
-        <v>1674.542044845438</v>
+        <v>1664.402623716546</v>
       </c>
       <c r="F4">
-        <v>2919.969223123148</v>
+        <v>2062.562932055133</v>
       </c>
       <c r="G4">
-        <v>8530</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -519,45 +534,45 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>2094.255239626178</v>
+        <v>2094.847121605158</v>
       </c>
       <c r="E5">
-        <v>1779.6805130783</v>
+        <v>1784.020288349707</v>
       </c>
       <c r="F5">
-        <v>2964.981238581805</v>
+        <v>2970.442093443431</v>
       </c>
       <c r="G5">
-        <v>8130</v>
+        <v>8068</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>2139.454554982668</v>
+        <v>2097.498961788019</v>
       </c>
       <c r="E6">
-        <v>1625.677652962645</v>
+        <v>1790.030987130527</v>
       </c>
       <c r="F6">
-        <v>5253.327082144429</v>
+        <v>2965.937018363914</v>
       </c>
       <c r="G6">
-        <v>6284</v>
+        <v>7987</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -565,22 +580,22 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>2190.40768801152</v>
+        <v>2120.447583356405</v>
       </c>
       <c r="E7">
-        <v>1716.789261397937</v>
+        <v>1880.603185148313</v>
       </c>
       <c r="F7">
-        <v>5556.318376064999</v>
+        <v>2994.916968518872</v>
       </c>
       <c r="G7">
-        <v>6138</v>
+        <v>7486</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -594,16 +609,16 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>2036.172144309533</v>
+        <v>2201.94916344533</v>
       </c>
       <c r="E8">
-        <v>1597.475170722365</v>
+        <v>1741.858674603995</v>
       </c>
       <c r="F8">
-        <v>2872.225193909877</v>
+        <v>5782.542181908672</v>
       </c>
       <c r="G8">
-        <v>6955</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -617,16 +632,108 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>2078.691136327394</v>
+        <v>2207.351582742057</v>
       </c>
       <c r="E9">
-        <v>1686.362337662391</v>
+        <v>1756.900334388553</v>
       </c>
       <c r="F9">
-        <v>2897.95372670126</v>
+        <v>5645.26797344752</v>
       </c>
       <c r="G9">
-        <v>6518</v>
+        <v>6165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>2239.701479656338</v>
+      </c>
+      <c r="E10">
+        <v>1871.028470787551</v>
+      </c>
+      <c r="F10">
+        <v>6017.496607009682</v>
+      </c>
+      <c r="G10">
+        <v>5809</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>2081.936303982277</v>
+      </c>
+      <c r="E11">
+        <v>1694.109791338248</v>
+      </c>
+      <c r="F11">
+        <v>2903.196461211689</v>
+      </c>
+      <c r="G11">
+        <v>6466</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>2083.956888765144</v>
+      </c>
+      <c r="E12">
+        <v>1714.14079801104</v>
+      </c>
+      <c r="F12">
+        <v>2910.003287357169</v>
+      </c>
+      <c r="G12">
+        <v>6568</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>2108.079725610248</v>
+      </c>
+      <c r="E13">
+        <v>1833.898119798687</v>
+      </c>
+      <c r="F13">
+        <v>2941.97580699658</v>
+      </c>
+      <c r="G13">
+        <v>6007</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/msy_resumo_cenarios_dbsra.xlsx
+++ b/Catch models/msy_resumo_cenarios_dbsra.xlsx
@@ -471,16 +471,16 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1896.769409607813</v>
+        <v>1218.986938957394</v>
       </c>
       <c r="E2">
-        <v>1581.59097671675</v>
+        <v>917.8743243933513</v>
       </c>
       <c r="F2">
-        <v>2046.507984910551</v>
+        <v>1410.055572900835</v>
       </c>
       <c r="G2">
-        <v>3352</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -494,16 +494,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>1895.789243182264</v>
+        <v>1219.736609997561</v>
       </c>
       <c r="E3">
-        <v>1591.736666665113</v>
+        <v>924.295667998769</v>
       </c>
       <c r="F3">
-        <v>2048.019297247105</v>
+        <v>1289.286137042821</v>
       </c>
       <c r="G3">
-        <v>3249</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -517,16 +517,16 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>1942.305860762551</v>
+        <v>1235.430765168215</v>
       </c>
       <c r="E4">
-        <v>1664.402623716546</v>
+        <v>927.4123239372808</v>
       </c>
       <c r="F4">
-        <v>2062.562932055133</v>
+        <v>1415.438084810834</v>
       </c>
       <c r="G4">
-        <v>2763</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -540,16 +540,16 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>2094.847121605158</v>
+        <v>1337.504959144467</v>
       </c>
       <c r="E5">
-        <v>1784.020288349707</v>
+        <v>1126.993719520127</v>
       </c>
       <c r="F5">
-        <v>2970.442093443431</v>
+        <v>1489.499044081904</v>
       </c>
       <c r="G5">
-        <v>8068</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -563,16 +563,16 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>2097.498961788019</v>
+        <v>1341.845049930966</v>
       </c>
       <c r="E6">
-        <v>1790.030987130527</v>
+        <v>1146.180293470113</v>
       </c>
       <c r="F6">
-        <v>2965.937018363914</v>
+        <v>1494.179151500089</v>
       </c>
       <c r="G6">
-        <v>7987</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -586,16 +586,16 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>2120.447583356405</v>
+        <v>1374.828057787021</v>
       </c>
       <c r="E7">
-        <v>1880.603185148313</v>
+        <v>1182.429248769567</v>
       </c>
       <c r="F7">
-        <v>2994.916968518872</v>
+        <v>1506.738615495821</v>
       </c>
       <c r="G7">
-        <v>7486</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -609,16 +609,16 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>2201.94916344533</v>
+        <v>1403.802879020193</v>
       </c>
       <c r="E8">
-        <v>1741.858674603995</v>
+        <v>1166.958912778817</v>
       </c>
       <c r="F8">
-        <v>5782.542181908672</v>
+        <v>4108.145522359886</v>
       </c>
       <c r="G8">
-        <v>6200</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -632,16 +632,16 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>2207.351582742057</v>
+        <v>1405.775491658624</v>
       </c>
       <c r="E9">
-        <v>1756.900334388553</v>
+        <v>1165.384938051262</v>
       </c>
       <c r="F9">
-        <v>5645.26797344752</v>
+        <v>4174.315778247571</v>
       </c>
       <c r="G9">
-        <v>6165</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -655,16 +655,16 @@
         <v>13</v>
       </c>
       <c r="D10">
-        <v>2239.701479656338</v>
+        <v>1428.855019271932</v>
       </c>
       <c r="E10">
-        <v>1871.028470787551</v>
+        <v>1224.528893382908</v>
       </c>
       <c r="F10">
-        <v>6017.496607009682</v>
+        <v>4118.132057459672</v>
       </c>
       <c r="G10">
-        <v>5809</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -678,16 +678,16 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>2081.936303982277</v>
+        <v>1230.762347646194</v>
       </c>
       <c r="E11">
-        <v>1694.109791338248</v>
+        <v>955.6205134377254</v>
       </c>
       <c r="F11">
-        <v>2903.196461211689</v>
+        <v>1418.617182715296</v>
       </c>
       <c r="G11">
-        <v>6466</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -701,16 +701,16 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>2083.956888765144</v>
+        <v>1234.048760229664</v>
       </c>
       <c r="E12">
-        <v>1714.14079801104</v>
+        <v>989.2641212387655</v>
       </c>
       <c r="F12">
-        <v>2910.003287357169</v>
+        <v>1356.389961688913</v>
       </c>
       <c r="G12">
-        <v>6568</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -724,16 +724,16 @@
         <v>13</v>
       </c>
       <c r="D13">
-        <v>2108.079725610248</v>
+        <v>1264.321932736402</v>
       </c>
       <c r="E13">
-        <v>1833.898119798687</v>
+        <v>1044.136251910876</v>
       </c>
       <c r="F13">
-        <v>2941.97580699658</v>
+        <v>1434.005114283734</v>
       </c>
       <c r="G13">
-        <v>6007</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/msy_resumo_cenarios_dbsra.xlsx
+++ b/Catch models/msy_resumo_cenarios_dbsra.xlsx
@@ -37,7 +37,7 @@
     <t>n_aceitos</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Jardim(1981-1994)</t>
+    <t>NN_CMSY_Jardim (1999)</t>
   </si>
   <si>
     <t>NN_CMSY</t>
@@ -46,52 +46,52 @@
     <t>M_Jardim(1981-1994)</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Santos(2005-2018)</t>
+    <t>NN_CMSY_Santos (2018)</t>
   </si>
   <si>
     <t>M_Santos(2005-2018)</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Vieira(1988-2018)</t>
+    <t>NN_CMSY_Vieira (2019)</t>
   </si>
   <si>
     <t>M_Vieira(1988-2018)</t>
   </si>
   <si>
-    <t>Target_switch_M_Jardim(1981-1994)</t>
+    <t>Target_switch_Jardim (1999)</t>
   </si>
   <si>
     <t>Target_switch</t>
   </si>
   <si>
-    <t>Target_switch_M_Santos(2005-2018)</t>
-  </si>
-  <si>
-    <t>Target_switch_M_Vieira(1988-2018)</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_M_Jardim(1981-1994)</t>
+    <t>Target_switch_Santos (2018)</t>
+  </si>
+  <si>
+    <t>Target_switch_Vieira (2019)</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Jardim (1999)</t>
   </si>
   <si>
     <t>Uninformative_bk</t>
   </si>
   <si>
-    <t>Uninformative_bk_M_Santos(2005-2018)</t>
-  </si>
-  <si>
-    <t>Uninformative_bk_M_Vieira(1988-2018)</t>
-  </si>
-  <si>
-    <t>zBRT_M_Jardim(1981-1994)</t>
+    <t>Uninformative_bk_Santos (2018)</t>
+  </si>
+  <si>
+    <t>Uninformative_bk_Vieira (2019)</t>
+  </si>
+  <si>
+    <t>zBRT_Jardim (1999)</t>
   </si>
   <si>
     <t>zBRT</t>
   </si>
   <si>
-    <t>zBRT_M_Santos(2005-2018)</t>
-  </si>
-  <si>
-    <t>zBRT_M_Vieira(1988-2018)</t>
+    <t>zBRT_Santos (2018)</t>
+  </si>
+  <si>
+    <t>zBRT_Vieira (2019)</t>
   </si>
 </sst>
 </file>
@@ -471,16 +471,16 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1218.986938957394</v>
+        <v>1619.335823732185</v>
       </c>
       <c r="E2">
-        <v>917.8743243933513</v>
+        <v>1223.881424856919</v>
       </c>
       <c r="F2">
-        <v>1410.055572900835</v>
+        <v>2015.997623812133</v>
       </c>
       <c r="G2">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -494,16 +494,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>1219.736609997561</v>
+        <v>1614.280032106527</v>
       </c>
       <c r="E3">
-        <v>924.295667998769</v>
+        <v>1176.948026002508</v>
       </c>
       <c r="F3">
-        <v>1289.286137042821</v>
+        <v>1879.065718455432</v>
       </c>
       <c r="G3">
-        <v>115</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -517,16 +517,16 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>1235.430765168215</v>
+        <v>1646.455910822204</v>
       </c>
       <c r="E4">
-        <v>927.4123239372808</v>
+        <v>1189.190416442509</v>
       </c>
       <c r="F4">
-        <v>1415.438084810834</v>
+        <v>2044.880085491651</v>
       </c>
       <c r="G4">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -540,16 +540,16 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>1337.504959144467</v>
+        <v>1703.69217956934</v>
       </c>
       <c r="E5">
-        <v>1126.993719520127</v>
+        <v>1372.491761234453</v>
       </c>
       <c r="F5">
-        <v>1489.499044081904</v>
+        <v>1897.51437192714</v>
       </c>
       <c r="G5">
-        <v>2960</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -563,16 +563,16 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>1341.845049930966</v>
+        <v>1689.691650199756</v>
       </c>
       <c r="E6">
-        <v>1146.180293470113</v>
+        <v>1420.416330073579</v>
       </c>
       <c r="F6">
-        <v>1494.179151500089</v>
+        <v>1901.667082821808</v>
       </c>
       <c r="G6">
-        <v>2869</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -586,16 +586,16 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>1374.828057787021</v>
+        <v>1779.714733372287</v>
       </c>
       <c r="E7">
-        <v>1182.429248769567</v>
+        <v>1513.226857017925</v>
       </c>
       <c r="F7">
-        <v>1506.738615495821</v>
+        <v>2015.80014922281</v>
       </c>
       <c r="G7">
-        <v>2020</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -609,16 +609,16 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>1403.802879020193</v>
+        <v>1885.944024244911</v>
       </c>
       <c r="E8">
-        <v>1166.958912778817</v>
+        <v>1591.185143711475</v>
       </c>
       <c r="F8">
-        <v>4108.145522359886</v>
+        <v>4371.008299309227</v>
       </c>
       <c r="G8">
-        <v>2743</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -632,16 +632,16 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>1405.775491658624</v>
+        <v>1885.59195028412</v>
       </c>
       <c r="E9">
-        <v>1165.384938051262</v>
+        <v>1598.615987764362</v>
       </c>
       <c r="F9">
-        <v>4174.315778247571</v>
+        <v>4064.065480070441</v>
       </c>
       <c r="G9">
-        <v>2759</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -655,16 +655,16 @@
         <v>13</v>
       </c>
       <c r="D10">
-        <v>1428.855019271932</v>
+        <v>1907.843899139607</v>
       </c>
       <c r="E10">
-        <v>1224.528893382908</v>
+        <v>1658.326533659113</v>
       </c>
       <c r="F10">
-        <v>4118.132057459672</v>
+        <v>5037.183619841665</v>
       </c>
       <c r="G10">
-        <v>1958</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -678,16 +678,16 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>1230.762347646194</v>
+        <v>1664.266437260831</v>
       </c>
       <c r="E11">
-        <v>955.6205134377254</v>
+        <v>1372.34336417967</v>
       </c>
       <c r="F11">
-        <v>1418.617182715296</v>
+        <v>2014.485534756329</v>
       </c>
       <c r="G11">
-        <v>521</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -701,16 +701,16 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>1234.048760229664</v>
+        <v>1667.193380813786</v>
       </c>
       <c r="E12">
-        <v>989.2641212387655</v>
+        <v>1297.975058933059</v>
       </c>
       <c r="F12">
-        <v>1356.389961688913</v>
+        <v>1891.05669847893</v>
       </c>
       <c r="G12">
-        <v>487</v>
+        <v>609</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -724,16 +724,16 @@
         <v>13</v>
       </c>
       <c r="D13">
-        <v>1264.321932736402</v>
+        <v>1718.719879904202</v>
       </c>
       <c r="E13">
-        <v>1044.136251910876</v>
+        <v>1437.087274843967</v>
       </c>
       <c r="F13">
-        <v>1434.005114283734</v>
+        <v>2015.191526504665</v>
       </c>
       <c r="G13">
-        <v>250</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/msy_resumo_cenarios_dbsra.xlsx
+++ b/Catch models/msy_resumo_cenarios_dbsra.xlsx
@@ -471,16 +471,16 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1619.335823732185</v>
+        <v>1708.684063534089</v>
       </c>
       <c r="E2">
-        <v>1223.881424856919</v>
+        <v>1300.884271090898</v>
       </c>
       <c r="F2">
-        <v>2015.997623812133</v>
+        <v>2028.391810603788</v>
       </c>
       <c r="G2">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -494,16 +494,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>1614.280032106527</v>
+        <v>1709.559722288294</v>
       </c>
       <c r="E3">
-        <v>1176.948026002508</v>
+        <v>1266.247664410434</v>
       </c>
       <c r="F3">
-        <v>1879.065718455432</v>
+        <v>2035.531151567974</v>
       </c>
       <c r="G3">
-        <v>142</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -517,16 +517,16 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>1646.455910822204</v>
+        <v>1723.751843001479</v>
       </c>
       <c r="E4">
-        <v>1189.190416442509</v>
+        <v>1359.403179748416</v>
       </c>
       <c r="F4">
-        <v>2044.880085491651</v>
+        <v>2049.381898989173</v>
       </c>
       <c r="G4">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -540,16 +540,16 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>1703.69217956934</v>
+        <v>1765.924500991997</v>
       </c>
       <c r="E5">
-        <v>1372.491761234453</v>
+        <v>1490.435222539403</v>
       </c>
       <c r="F5">
-        <v>1897.51437192714</v>
+        <v>1987.696909501695</v>
       </c>
       <c r="G5">
-        <v>983</v>
+        <v>925</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -563,16 +563,16 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>1689.691650199756</v>
+        <v>1779.892877000475</v>
       </c>
       <c r="E6">
-        <v>1420.416330073579</v>
+        <v>1515.356564447556</v>
       </c>
       <c r="F6">
-        <v>1901.667082821808</v>
+        <v>2018.118535630843</v>
       </c>
       <c r="G6">
-        <v>957</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -586,16 +586,16 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>1779.714733372287</v>
+        <v>1809.239947653631</v>
       </c>
       <c r="E7">
-        <v>1513.226857017925</v>
+        <v>1592.16028491316</v>
       </c>
       <c r="F7">
-        <v>2015.80014922281</v>
+        <v>2018.639912913117</v>
       </c>
       <c r="G7">
-        <v>634</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -609,16 +609,16 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>1885.944024244911</v>
+        <v>1918.338164500087</v>
       </c>
       <c r="E8">
-        <v>1591.185143711475</v>
+        <v>1660.966386973631</v>
       </c>
       <c r="F8">
-        <v>4371.008299309227</v>
+        <v>4267.149540232636</v>
       </c>
       <c r="G8">
-        <v>2601</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -632,16 +632,16 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>1885.59195028412</v>
+        <v>1920.761358638109</v>
       </c>
       <c r="E9">
-        <v>1598.615987764362</v>
+        <v>1679.038645894988</v>
       </c>
       <c r="F9">
-        <v>4064.065480070441</v>
+        <v>4209.683934400912</v>
       </c>
       <c r="G9">
-        <v>2644</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -655,16 +655,16 @@
         <v>13</v>
       </c>
       <c r="D10">
-        <v>1907.843899139607</v>
+        <v>1932.920679434467</v>
       </c>
       <c r="E10">
-        <v>1658.326533659113</v>
+        <v>1721.930093807285</v>
       </c>
       <c r="F10">
-        <v>5037.183619841665</v>
+        <v>5310.358291766477</v>
       </c>
       <c r="G10">
-        <v>1932</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -678,13 +678,13 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>1664.266437260831</v>
+        <v>1733.742440530326</v>
       </c>
       <c r="E11">
-        <v>1372.34336417967</v>
+        <v>1480.171469687042</v>
       </c>
       <c r="F11">
-        <v>2014.485534756329</v>
+        <v>2018.431540066693</v>
       </c>
       <c r="G11">
         <v>627</v>
@@ -701,16 +701,16 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>1667.193380813786</v>
+        <v>1744.910032740764</v>
       </c>
       <c r="E12">
-        <v>1297.975058933059</v>
+        <v>1431.961778236544</v>
       </c>
       <c r="F12">
-        <v>1891.05669847893</v>
+        <v>2034.32331802209</v>
       </c>
       <c r="G12">
-        <v>609</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -724,16 +724,16 @@
         <v>13</v>
       </c>
       <c r="D13">
-        <v>1718.719879904202</v>
+        <v>1776.07142858124</v>
       </c>
       <c r="E13">
-        <v>1437.087274843967</v>
+        <v>1560.882264480264</v>
       </c>
       <c r="F13">
-        <v>2015.191526504665</v>
+        <v>2036.431411445723</v>
       </c>
       <c r="G13">
-        <v>367</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/msy_resumo_cenarios_dbsra.xlsx
+++ b/Catch models/msy_resumo_cenarios_dbsra.xlsx
@@ -471,16 +471,16 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1708.684063534089</v>
+        <v>1696.850683904675</v>
       </c>
       <c r="E2">
-        <v>1300.884271090898</v>
+        <v>1354.873080015484</v>
       </c>
       <c r="F2">
-        <v>2028.391810603788</v>
+        <v>1950.388645628003</v>
       </c>
       <c r="G2">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -494,16 +494,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>1709.559722288294</v>
+        <v>1700.956682330074</v>
       </c>
       <c r="E3">
-        <v>1266.247664410434</v>
+        <v>1291.853675833786</v>
       </c>
       <c r="F3">
-        <v>2035.531151567974</v>
+        <v>1940.223201231468</v>
       </c>
       <c r="G3">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -517,16 +517,16 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>1723.751843001479</v>
+        <v>1767.11944911371</v>
       </c>
       <c r="E4">
-        <v>1359.403179748416</v>
+        <v>1360.82486375688</v>
       </c>
       <c r="F4">
-        <v>2049.381898989173</v>
+        <v>1949.692715692759</v>
       </c>
       <c r="G4">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -540,16 +540,16 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>1765.924500991997</v>
+        <v>1784.283712225263</v>
       </c>
       <c r="E5">
-        <v>1490.435222539403</v>
+        <v>1518.496886906868</v>
       </c>
       <c r="F5">
-        <v>1987.696909501695</v>
+        <v>1940.173157832319</v>
       </c>
       <c r="G5">
-        <v>925</v>
+        <v>957</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -563,16 +563,16 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>1779.892877000475</v>
+        <v>1794.76870347512</v>
       </c>
       <c r="E6">
-        <v>1515.356564447556</v>
+        <v>1525.423854101622</v>
       </c>
       <c r="F6">
-        <v>2018.118535630843</v>
+        <v>1945.524657936332</v>
       </c>
       <c r="G6">
-        <v>915</v>
+        <v>923</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -586,16 +586,16 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>1809.239947653631</v>
+        <v>1823.742474777411</v>
       </c>
       <c r="E7">
-        <v>1592.16028491316</v>
+        <v>1601.349058998593</v>
       </c>
       <c r="F7">
-        <v>2018.639912913117</v>
+        <v>1958.959221091168</v>
       </c>
       <c r="G7">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -609,16 +609,16 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>1918.338164500087</v>
+        <v>1937.033007604601</v>
       </c>
       <c r="E8">
-        <v>1660.966386973631</v>
+        <v>1686.761622314374</v>
       </c>
       <c r="F8">
-        <v>4267.149540232636</v>
+        <v>4145.43755607229</v>
       </c>
       <c r="G8">
-        <v>2650</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -632,16 +632,16 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>1920.761358638109</v>
+        <v>1942.500674549699</v>
       </c>
       <c r="E9">
-        <v>1679.038645894988</v>
+        <v>1699.756208731219</v>
       </c>
       <c r="F9">
-        <v>4209.683934400912</v>
+        <v>4469.785983526052</v>
       </c>
       <c r="G9">
-        <v>2633</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -655,16 +655,16 @@
         <v>13</v>
       </c>
       <c r="D10">
-        <v>1932.920679434467</v>
+        <v>1953.552927866017</v>
       </c>
       <c r="E10">
-        <v>1721.930093807285</v>
+        <v>1748.428582592553</v>
       </c>
       <c r="F10">
-        <v>5310.358291766477</v>
+        <v>4827.306308731374</v>
       </c>
       <c r="G10">
-        <v>1936</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -678,16 +678,16 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>1733.742440530326</v>
+        <v>1747.040288031871</v>
       </c>
       <c r="E11">
-        <v>1480.171469687042</v>
+        <v>1486.154822809619</v>
       </c>
       <c r="F11">
-        <v>2018.431540066693</v>
+        <v>1921.975948387453</v>
       </c>
       <c r="G11">
-        <v>627</v>
+        <v>583</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -701,16 +701,16 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>1744.910032740764</v>
+        <v>1759.620244365128</v>
       </c>
       <c r="E12">
-        <v>1431.961778236544</v>
+        <v>1443.090415175505</v>
       </c>
       <c r="F12">
-        <v>2034.32331802209</v>
+        <v>1937.590956103033</v>
       </c>
       <c r="G12">
-        <v>555</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -724,16 +724,16 @@
         <v>13</v>
       </c>
       <c r="D13">
-        <v>1776.07142858124</v>
+        <v>1791.016931092923</v>
       </c>
       <c r="E13">
-        <v>1560.882264480264</v>
+        <v>1577.997008427687</v>
       </c>
       <c r="F13">
-        <v>2036.431411445723</v>
+        <v>1951.85301680473</v>
       </c>
       <c r="G13">
-        <v>315</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
